--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_10.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03056456785834777</v>
+        <v>0.02604623186847839</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008451193563359072</v>
+        <v>0.008445755456178603</v>
       </c>
       <c r="C2" t="n">
-        <v>63630810</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63630810</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>42982895</v>
+        <v>4054422</v>
       </c>
       <c r="L2" t="n">
-        <v>22275455</v>
+        <v>1769135</v>
       </c>
       <c r="M2" t="n">
-        <v>5044302</v>
+        <v>300022</v>
       </c>
       <c r="N2" t="n">
-        <v>225482</v>
+        <v>8003</v>
       </c>
       <c r="O2" t="n">
-        <v>3020990</v>
+        <v>170236</v>
       </c>
       <c r="P2" t="n">
-        <v>1203849</v>
+        <v>65672</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999849200248718</v>
+        <v>0.9999593496322632</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8226046562194824</v>
+        <v>0.7346255779266357</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6753430366516113</v>
+        <v>0.5481702089309692</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5965925455093384</v>
+        <v>0.4314659535884857</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2122756987810135</v>
+        <v>0.04942503198981285</v>
       </c>
       <c r="V2" t="n">
-        <v>0.654330313205719</v>
+        <v>0.4732826948165894</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7572277188301086</v>
+        <v>0.6194595098495483</v>
       </c>
       <c r="X2" t="n">
-        <v>63630810</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63630810</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>48394651</v>
+        <v>4789433</v>
       </c>
       <c r="AG2" t="n">
-        <v>30110592</v>
+        <v>3027015</v>
       </c>
       <c r="AH2" t="n">
-        <v>8040827</v>
+        <v>807060</v>
       </c>
       <c r="AI2" t="n">
-        <v>592793</v>
+        <v>59367</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4601871</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1802011</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559258222579956</v>
+        <v>0.9549785256385803</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116288423538208</v>
+        <v>0.912082850933075</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.857900857925415</v>
+        <v>0.8579939603805542</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6614111065864563</v>
+        <v>0.6605360507965088</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019286632537842</v>
+        <v>0.90191650390625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314581155776978</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.007997050598701535</v>
+        <v>0.006667084993269943</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002024183214990091</v>
+        <v>0.002023579242838846</v>
       </c>
       <c r="C3" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>42982895</v>
+        <v>4054422</v>
       </c>
       <c r="E3" t="n">
-        <v>7270881</v>
+        <v>910012</v>
       </c>
       <c r="F3" t="n">
-        <v>241090</v>
+        <v>32228</v>
       </c>
       <c r="G3" t="n">
-        <v>29951</v>
+        <v>3707</v>
       </c>
       <c r="H3" t="n">
-        <v>16834</v>
+        <v>2368</v>
       </c>
       <c r="I3" t="n">
-        <v>1457</v>
+        <v>246</v>
       </c>
       <c r="J3" t="n">
-        <v>100960232</v>
+        <v>10069362</v>
       </c>
       <c r="K3" t="n">
-        <v>104779520</v>
+        <v>9948400</v>
       </c>
       <c r="L3" t="n">
-        <v>120787212</v>
+        <v>11629404</v>
       </c>
       <c r="M3" t="n">
-        <v>151797679</v>
+        <v>15078143</v>
       </c>
       <c r="N3" t="n">
-        <v>162858102</v>
+        <v>16172103</v>
       </c>
       <c r="O3" t="n">
-        <v>157890282</v>
+        <v>15714606</v>
       </c>
       <c r="P3" t="n">
-        <v>162270756</v>
+        <v>16181852</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8504191637039185</v>
+        <v>0.8103997707366943</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6730490922927856</v>
+        <v>0.5315295457839966</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5375751852989197</v>
+        <v>0.3183176219463348</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2513266801834106</v>
+        <v>0.0889439657330513</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5916793942451477</v>
+        <v>0.3325324654579163</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6220535039901733</v>
+        <v>0.3388560712337494</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>48394651</v>
+        <v>4789433</v>
       </c>
       <c r="Z3" t="n">
-        <v>1993417</v>
+        <v>198166</v>
       </c>
       <c r="AA3" t="n">
-        <v>85791</v>
+        <v>8476</v>
       </c>
       <c r="AB3" t="n">
-        <v>68679</v>
+        <v>6874</v>
       </c>
       <c r="AC3" t="n">
-        <v>348</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100961190</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>111817518</v>
+        <v>11187217</v>
       </c>
       <c r="AG3" t="n">
-        <v>128576818</v>
+        <v>12795836</v>
       </c>
       <c r="AH3" t="n">
-        <v>153876716</v>
+        <v>15339900</v>
       </c>
       <c r="AI3" t="n">
-        <v>163391371</v>
+        <v>16295512</v>
       </c>
       <c r="AJ3" t="n">
-        <v>158985826</v>
+        <v>15853902</v>
       </c>
       <c r="AK3" t="n">
-        <v>162524116</v>
+        <v>16208926</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9574910998344421</v>
+        <v>0.957314133644104</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097864031791687</v>
+        <v>0.9094545841217041</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8569172024726868</v>
+        <v>0.8562752604484558</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6607387661933899</v>
+        <v>0.6597946286201477</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013046026229858</v>
+        <v>0.900970458984375</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311361312866211</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06898720185764785</v>
+        <v>0.06034233411560776</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03196319628040224</v>
+        <v>0.03194845442669837</v>
       </c>
       <c r="C4" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>8566708</v>
+        <v>1324753</v>
       </c>
       <c r="E4" t="n">
-        <v>22275455</v>
+        <v>1769135</v>
       </c>
       <c r="F4" t="n">
-        <v>1875492</v>
+        <v>179893</v>
       </c>
       <c r="G4" t="n">
-        <v>134800</v>
+        <v>23142</v>
       </c>
       <c r="H4" t="n">
-        <v>218539</v>
+        <v>27603</v>
       </c>
       <c r="I4" t="n">
-        <v>25259</v>
+        <v>3827</v>
       </c>
       <c r="J4" t="n">
-        <v>958</v>
+        <v>258</v>
       </c>
       <c r="K4" t="n">
-        <v>9269294</v>
+        <v>1464610</v>
       </c>
       <c r="L4" t="n">
-        <v>10708457</v>
+        <v>1458211</v>
       </c>
       <c r="M4" t="n">
-        <v>3410886</v>
+        <v>395333</v>
       </c>
       <c r="N4" t="n">
-        <v>836731</v>
+        <v>153919</v>
       </c>
       <c r="O4" t="n">
-        <v>1595929</v>
+        <v>189456</v>
       </c>
       <c r="P4" t="n">
-        <v>385962</v>
+        <v>40343</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999924302101135</v>
+        <v>0.9999796748161316</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8362806439399719</v>
+        <v>0.7706544995307922</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6741941571235657</v>
+        <v>0.539721667766571</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5655483603477478</v>
+        <v>0.3663542866706848</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2301564812660217</v>
+        <v>0.06354108452796936</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6214298009872437</v>
+        <v>0.3906152844429016</v>
       </c>
       <c r="W4" t="n">
-        <v>0.683016836643219</v>
+        <v>0.4380761682987213</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2083830</v>
+        <v>211003</v>
       </c>
       <c r="Z4" t="n">
-        <v>30110592</v>
+        <v>3027015</v>
       </c>
       <c r="AA4" t="n">
-        <v>834124</v>
+        <v>83549</v>
       </c>
       <c r="AB4" t="n">
-        <v>55675</v>
+        <v>5619</v>
       </c>
       <c r="AC4" t="n">
-        <v>11430</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2231296</v>
+        <v>225793</v>
       </c>
       <c r="AG4" t="n">
-        <v>2918851</v>
+        <v>291779</v>
       </c>
       <c r="AH4" t="n">
-        <v>1331849</v>
+        <v>133576</v>
       </c>
       <c r="AI4" t="n">
-        <v>303462</v>
+        <v>30510</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500385</v>
+        <v>50160</v>
       </c>
       <c r="AK4" t="n">
-        <v>132602</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567078351974487</v>
+        <v>0.9561448693275452</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107067584991455</v>
+        <v>0.9107667803764343</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8574087619781494</v>
+        <v>0.8571337461471558</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6610747575759888</v>
+        <v>0.6601651310920715</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016165137290955</v>
+        <v>0.9014432430267334</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312970638275146</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="D5" t="n">
-        <v>502873</v>
+        <v>104467</v>
       </c>
       <c r="E5" t="n">
-        <v>2770696</v>
+        <v>418166</v>
       </c>
       <c r="F5" t="n">
-        <v>5044302</v>
+        <v>300022</v>
       </c>
       <c r="G5" t="n">
-        <v>269608</v>
+        <v>40678</v>
       </c>
       <c r="H5" t="n">
-        <v>711471</v>
+        <v>68023</v>
       </c>
       <c r="I5" t="n">
-        <v>84345</v>
+        <v>11114</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7560291</v>
+        <v>948568</v>
       </c>
       <c r="L5" t="n">
-        <v>10820876</v>
+        <v>1559250</v>
       </c>
       <c r="M5" t="n">
-        <v>4339133</v>
+        <v>642502</v>
       </c>
       <c r="N5" t="n">
-        <v>671685</v>
+        <v>81975</v>
       </c>
       <c r="O5" t="n">
-        <v>2084799</v>
+        <v>341702</v>
       </c>
       <c r="P5" t="n">
-        <v>731433</v>
+        <v>128133</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999994158744812</v>
+        <v>0.9999842643737793</v>
       </c>
       <c r="R5" t="n">
-        <v>0.897749662399292</v>
+        <v>0.8529984354972839</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8691957592964172</v>
+        <v>0.8161877989768982</v>
       </c>
       <c r="T5" t="n">
-        <v>0.952913761138916</v>
+        <v>0.9367790818214417</v>
       </c>
       <c r="U5" t="n">
-        <v>0.990835428237915</v>
+        <v>0.985630214214325</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9776372313499451</v>
+        <v>0.9676438570022583</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9932111501693726</v>
+        <v>0.9897370934486389</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>81333</v>
+        <v>8141</v>
       </c>
       <c r="Z5" t="n">
-        <v>862543</v>
+        <v>87332</v>
       </c>
       <c r="AA5" t="n">
-        <v>8040827</v>
+        <v>807060</v>
       </c>
       <c r="AB5" t="n">
-        <v>100071</v>
+        <v>10049</v>
       </c>
       <c r="AC5" t="n">
-        <v>292331</v>
+        <v>29309</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2148535</v>
+        <v>213557</v>
       </c>
       <c r="AG5" t="n">
-        <v>2985739</v>
+        <v>301370</v>
       </c>
       <c r="AH5" t="n">
-        <v>1342608</v>
+        <v>135464</v>
       </c>
       <c r="AI5" t="n">
-        <v>304374</v>
+        <v>30611</v>
       </c>
       <c r="AJ5" t="n">
-        <v>503918</v>
+        <v>50697</v>
       </c>
       <c r="AK5" t="n">
-        <v>133271</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973389744758606</v>
+        <v>0.9732365012168884</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641258716583252</v>
+        <v>0.9638676047325134</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837509989738464</v>
+        <v>0.9836111068725586</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963070154190063</v>
+        <v>0.9962767362594604</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938982129096985</v>
+        <v>0.9938561916351318</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983846545219421</v>
+        <v>0.9983761310577393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>149203</v>
+        <v>21392</v>
       </c>
       <c r="E6" t="n">
-        <v>197673</v>
+        <v>27412</v>
       </c>
       <c r="F6" t="n">
-        <v>214691</v>
+        <v>24491</v>
       </c>
       <c r="G6" t="n">
-        <v>225482</v>
+        <v>8003</v>
       </c>
       <c r="H6" t="n">
-        <v>97539</v>
+        <v>7466</v>
       </c>
       <c r="I6" t="n">
-        <v>12454</v>
+        <v>1204</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65613</v>
+        <v>6613</v>
       </c>
       <c r="Z6" t="n">
-        <v>53974</v>
+        <v>5390</v>
       </c>
       <c r="AA6" t="n">
-        <v>109902</v>
+        <v>11097</v>
       </c>
       <c r="AB6" t="n">
-        <v>592793</v>
+        <v>59367</v>
       </c>
       <c r="AC6" t="n">
-        <v>70074</v>
+        <v>7030</v>
       </c>
       <c r="AD6" t="n">
-        <v>4811</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>259</v>
+        <v>93</v>
       </c>
       <c r="D7" t="n">
-        <v>47813</v>
+        <v>13176</v>
       </c>
       <c r="E7" t="n">
-        <v>427145</v>
+        <v>92382</v>
       </c>
       <c r="F7" t="n">
-        <v>992259</v>
+        <v>140073</v>
       </c>
       <c r="G7" t="n">
-        <v>354876</v>
+        <v>72026</v>
       </c>
       <c r="H7" t="n">
-        <v>3020990</v>
+        <v>170236</v>
       </c>
       <c r="I7" t="n">
-        <v>262447</v>
+        <v>23952</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>240</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8107</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>298715</v>
+        <v>30121</v>
       </c>
       <c r="AB7" t="n">
-        <v>76375</v>
+        <v>7701</v>
       </c>
       <c r="AC7" t="n">
-        <v>4601871</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120481</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>278</v>
+        <v>62</v>
       </c>
       <c r="D8" t="n">
-        <v>2697</v>
+        <v>822</v>
       </c>
       <c r="E8" t="n">
-        <v>42062</v>
+        <v>10239</v>
       </c>
       <c r="F8" t="n">
-        <v>87354</v>
+        <v>18648</v>
       </c>
       <c r="G8" t="n">
-        <v>47496</v>
+        <v>14366</v>
       </c>
       <c r="H8" t="n">
-        <v>551546</v>
+        <v>83996</v>
       </c>
       <c r="I8" t="n">
-        <v>1203849</v>
+        <v>65672</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3317</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2662</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126202</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1802011</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
